--- a/data/trans_orig/IMC-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMC Adultos</t>
+          <t>IMC Adultos (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25,37; 26,33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26,17; 27,14</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25,69; 26,82</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26,01; 27,43</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,07; 25,1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,42; 26,71</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,89; 26,23</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>25,36; 26,45</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>24,87; 25,59</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25,96; 26,77</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>25,45; 26,33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>26,19; 27,14</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25,67; 26,85</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26,06; 27,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,11; 25,08</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,47; 26,74</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24,85; 26,14</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25,42; 26,49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24,9; 25,63</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25,94; 26,75</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25,42; 26,3</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,92; 26,79</t>
+          <t>25,9; 26,81</t>
         </is>
       </c>
     </row>
@@ -861,57 +861,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,7; 26,5</t>
+          <t>25,65; 26,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,87; 26,61</t>
+          <t>25,85; 26,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,45; 27,52</t>
+          <t>26,48; 27,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,3; 26,11</t>
+          <t>25,31; 26,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,9; 26,85</t>
+          <t>25,92; 26,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 26,92</t>
+          <t>25,96; 26,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,45; 26,2</t>
+          <t>25,46; 26,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,44; 25,98</t>
+          <t>25,46; 26,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,95; 26,53</t>
+          <t>25,94; 26,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,02; 26,65</t>
+          <t>26,03; 26,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,1; 26,77</t>
+          <t>26,11; 26,79</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,23; 26,01</t>
+          <t>25,25; 26,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,53; 27,37</t>
+          <t>26,54; 27,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 27,83</t>
+          <t>26,77; 27,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,01; 25,99</t>
+          <t>25,04; 26,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,78; 26,97</t>
+          <t>25,73; 26,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,43; 26,59</t>
+          <t>25,42; 26,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 27,02</t>
+          <t>26,08; 27,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,26; 25,88</t>
+          <t>25,26; 25,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,24; 26,97</t>
+          <t>26,29; 27,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,91; 26,61</t>
+          <t>25,86; 26,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,55; 27,24</t>
+          <t>26,55; 27,28</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,91; 26,54</t>
+          <t>25,92; 26,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,67; 27,54</t>
+          <t>26,68; 27,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 27,31</t>
+          <t>26,33; 27,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,27; 27,3</t>
+          <t>26,26; 27,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,73; 25,61</t>
+          <t>24,69; 25,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 26,78</t>
+          <t>25,78; 26,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,39; 26,54</t>
+          <t>25,36; 26,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,12; 25,93</t>
+          <t>25,13; 25,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,44; 25,97</t>
+          <t>25,4; 25,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,34; 27,07</t>
+          <t>26,38; 27,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,98; 26,75</t>
+          <t>25,95; 26,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,74; 26,38</t>
+          <t>25,74; 26,46</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 26,68</t>
+          <t>25,75; 26,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,13; 27,24</t>
+          <t>26,08; 27,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,71; 26,86</t>
+          <t>25,73; 26,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,64; 26,48</t>
+          <t>25,65; 26,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,28; 26,81</t>
+          <t>25,36; 26,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,92; 26,41</t>
+          <t>24,95; 26,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 27,75</t>
+          <t>26,6; 27,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,66; 26,45</t>
+          <t>25,62; 26,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,66; 26,61</t>
+          <t>25,69; 26,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,72; 26,59</t>
+          <t>25,68; 26,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,3; 27,1</t>
+          <t>26,35; 27,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,76; 26,32</t>
+          <t>25,73; 26,3</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,62; 26,45</t>
+          <t>25,63; 26,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,08; 28,15</t>
+          <t>27,05; 28,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,18; 27,31</t>
+          <t>26,2; 27,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,68; 27,74</t>
+          <t>26,66; 27,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,97; 25,97</t>
+          <t>24,98; 26,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,3; 27,6</t>
+          <t>26,28; 27,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,52; 26,75</t>
+          <t>25,58; 26,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,1; 26,02</t>
+          <t>25,08; 26,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,4; 26,08</t>
+          <t>25,41; 26,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,82; 27,67</t>
+          <t>26,81; 27,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,06; 26,88</t>
+          <t>26,0; 26,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,05; 26,79</t>
+          <t>26,04; 26,79</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,82; 26,41</t>
+          <t>25,84; 26,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,27; 26,87</t>
+          <t>26,26; 26,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,78; 26,44</t>
+          <t>25,82; 26,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,98; 26,86</t>
+          <t>25,97; 26,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,17; 25,93</t>
+          <t>25,16; 25,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,97; 26,78</t>
+          <t>25,99; 26,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,61; 25,46</t>
+          <t>24,63; 25,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,42; 30,86</t>
+          <t>25,43; 31,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,56; 26,03</t>
+          <t>25,58; 26,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,25; 26,73</t>
+          <t>26,22; 26,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,3; 25,81</t>
+          <t>25,3; 25,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 29,58</t>
+          <t>25,87; 29,6</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,98; 26,57</t>
+          <t>25,98; 26,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,19; 26,74</t>
+          <t>26,17; 26,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,5; 27,17</t>
+          <t>26,51; 27,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,2; 28,93</t>
+          <t>26,21; 28,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,72; 25,51</t>
+          <t>24,76; 25,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,72; 26,47</t>
+          <t>25,71; 26,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,02; 26,78</t>
+          <t>26,03; 26,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,79; 26,38</t>
+          <t>25,77; 26,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,44; 25,91</t>
+          <t>25,44; 25,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,02; 26,48</t>
+          <t>26,02; 26,49</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,35; 26,84</t>
+          <t>26,34; 26,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,11; 28,12</t>
+          <t>26,11; 28,24</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,14</t>
+          <t>25,89; 26,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,51; 26,8</t>
+          <t>26,51; 26,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,32; 26,62</t>
+          <t>26,31; 26,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,61; 27,72</t>
+          <t>26,61; 27,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,22; 25,54</t>
+          <t>25,21; 25,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,1; 26,45</t>
+          <t>26,08; 26,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,81; 26,17</t>
+          <t>25,81; 26,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,82; 27,81</t>
+          <t>25,83; 27,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,59; 25,79</t>
+          <t>25,59; 25,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,34; 26,57</t>
+          <t>26,35; 26,58</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26,09; 26,34</t>
+          <t>26,12; 26,35</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26,28; 27,48</t>
+          <t>26,26; 27,43</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IMC-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,78</t>
+          <t>26,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,89</t>
+          <t>25,97</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,35</t>
+          <t>26,4</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,37; 26,33</t>
+          <t>25,43; 26,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,17; 27,14</t>
+          <t>26,15; 27,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,69; 26,82</t>
+          <t>25,7; 26,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,01; 27,43</t>
+          <t>26,27; 27,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,07; 25,1</t>
+          <t>24,14; 25,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,42; 26,71</t>
+          <t>25,44; 26,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,89; 26,23</t>
+          <t>24,86; 26,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,36; 26,45</t>
+          <t>25,45; 26,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,87; 25,59</t>
+          <t>24,86; 25,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,96; 26,77</t>
+          <t>25,95; 26,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,45; 26,33</t>
+          <t>25,42; 26,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,9; 26,81</t>
+          <t>26,03; 26,77</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,02</t>
+          <t>27,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,83</t>
+          <t>25,8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,43</t>
+          <t>26,42</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,43; 26,13</t>
+          <t>25,39; 26,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,65; 26,48</t>
+          <t>25,72; 26,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,85; 26,63</t>
+          <t>25,88; 26,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,48; 27,57</t>
+          <t>26,51; 27,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,31; 26,19</t>
+          <t>25,31; 26,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,92; 26,86</t>
+          <t>25,9; 26,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,96; 26,88</t>
+          <t>25,98; 26,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 26,19</t>
+          <t>25,41; 26,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 26,01</t>
+          <t>25,44; 26,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,94; 26,54</t>
+          <t>25,95; 26,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26,03; 26,62</t>
+          <t>26,06; 26,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,11; 26,79</t>
+          <t>26,12; 26,78</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,29</t>
+          <t>27,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,57</t>
+          <t>26,62</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,91</t>
+          <t>26,99</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,25; 26,01</t>
+          <t>25,2; 25,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,54; 27,36</t>
+          <t>26,55; 27,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,13; 26,98</t>
+          <t>26,16; 27,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,77; 27,87</t>
+          <t>26,93; 27,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,04; 26,06</t>
+          <t>25,06; 26,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,73; 26,81</t>
+          <t>25,71; 26,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 26,5</t>
+          <t>25,43; 26,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,08; 27,01</t>
+          <t>26,19; 27,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,26; 25,9</t>
+          <t>25,25; 25,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 27,01</t>
+          <t>26,26; 26,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,86; 26,57</t>
+          <t>25,92; 26,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,55; 27,28</t>
+          <t>26,68; 27,37</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,75</t>
+          <t>26,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,55</t>
+          <t>25,56</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>26,05</t>
+          <t>26,06</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 26,58</t>
+          <t>25,89; 26,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,68; 27,58</t>
+          <t>26,72; 27,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 27,37</t>
+          <t>26,3; 27,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,26; 27,35</t>
+          <t>26,15; 27,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 25,6</t>
+          <t>24,77; 25,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,78; 26,82</t>
+          <t>25,75; 26,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,36; 26,55</t>
+          <t>25,37; 26,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,13; 25,97</t>
+          <t>25,11; 26,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 25,96</t>
+          <t>25,45; 25,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,38; 27,05</t>
+          <t>26,37; 27,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,95; 26,73</t>
+          <t>25,98; 26,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,74; 26,46</t>
+          <t>25,69; 26,45</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,04</t>
+          <t>25,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,03</t>
+          <t>25,98</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,03</t>
+          <t>25,96</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 26,75</t>
+          <t>25,73; 26,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,08; 27,29</t>
+          <t>26,16; 27,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,73; 26,83</t>
+          <t>25,75; 26,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,65; 26,49</t>
+          <t>25,53; 26,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,36; 26,92</t>
+          <t>25,34; 26,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,95; 26,43</t>
+          <t>24,85; 26,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 27,74</t>
+          <t>26,52; 27,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,62; 26,44</t>
+          <t>25,56; 26,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,69; 26,63</t>
+          <t>25,66; 26,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,68; 26,6</t>
+          <t>25,74; 26,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,35; 27,13</t>
+          <t>26,33; 27,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,73; 26,3</t>
+          <t>25,68; 26,26</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,17</t>
+          <t>27,13</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,56</t>
+          <t>25,65</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,4</t>
+          <t>26,41</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,63; 26,46</t>
+          <t>25,56; 26,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,05; 28,13</t>
+          <t>27,09; 28,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,2; 27,28</t>
+          <t>26,21; 27,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,66; 27,8</t>
+          <t>26,7; 27,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,98; 26,03</t>
+          <t>24,97; 26,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,28; 27,57</t>
+          <t>26,31; 27,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,58; 26,86</t>
+          <t>25,5; 26,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,08; 26,01</t>
+          <t>25,23; 26,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,41; 26,08</t>
+          <t>25,4; 26,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,81; 27,64</t>
+          <t>26,84; 27,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,0; 26,84</t>
+          <t>26,01; 26,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26,04; 26,79</t>
+          <t>26,11; 26,81</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,38</t>
+          <t>26,45</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,7</t>
+          <t>25,65</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,14</t>
+          <t>26,04</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,84; 26,38</t>
+          <t>25,81; 26,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,26; 26,86</t>
+          <t>26,27; 26,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,82; 26,45</t>
+          <t>25,8; 26,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,97; 26,81</t>
+          <t>26,03; 26,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,16; 25,94</t>
+          <t>25,12; 25,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,99; 26,79</t>
+          <t>25,95; 26,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,63; 25,47</t>
+          <t>24,62; 25,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,43; 31,05</t>
+          <t>25,29; 25,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,58; 26,05</t>
+          <t>25,55; 26,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,22; 26,71</t>
+          <t>26,24; 26,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25,3; 25,8</t>
+          <t>25,3; 25,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 29,6</t>
+          <t>25,79; 26,31</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27,33</t>
+          <t>26,18</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26,07</t>
+          <t>26,08</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,79</t>
+          <t>26,13</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,98; 26,56</t>
+          <t>26,01; 26,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26,17; 26,72</t>
+          <t>26,17; 26,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,51; 27,17</t>
+          <t>26,5; 27,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,21; 28,7</t>
+          <t>25,92; 26,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,76; 25,45</t>
+          <t>24,75; 25,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,71; 26,46</t>
+          <t>25,73; 26,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,03; 26,75</t>
+          <t>25,98; 26,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,77; 26,37</t>
+          <t>25,79; 26,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,44; 25,89</t>
+          <t>25,44; 25,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,02; 26,49</t>
+          <t>26,01; 26,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26,34; 26,86</t>
+          <t>26,33; 26,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,11; 28,24</t>
+          <t>25,92; 26,35</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26,93</t>
+          <t>26,64</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26,36</t>
+          <t>25,9</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,64</t>
+          <t>26,26</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,15</t>
+          <t>25,9; 26,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,51; 26,79</t>
+          <t>26,53; 26,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26,31; 26,62</t>
+          <t>26,32; 26,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26,61; 27,63</t>
+          <t>26,47; 26,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,21; 25,55</t>
+          <t>25,22; 25,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,08; 26,45</t>
+          <t>26,07; 26,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,81; 26,18</t>
+          <t>25,82; 26,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,83; 27,57</t>
+          <t>25,77; 26,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25,59; 25,8</t>
+          <t>25,59; 25,79</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,35; 26,58</t>
+          <t>26,33; 26,58</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26,12; 26,35</t>
+          <t>26,11; 26,34</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26,26; 27,43</t>
+          <t>26,16; 26,37</t>
         </is>
       </c>
     </row>
